--- a/onreview_lifts.xlsx
+++ b/onreview_lifts.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Liftlər" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +25,37 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCE6F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +63,41 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +463,2542 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="35" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Liftin modeli (indeksi)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Bina</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Qeydiyyat nömrəsi</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Zavod nömrəsi</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Servis təşkilatının adı</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>İstehsal tarixi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>GeN2</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>wyndhamgardenbaku</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>43854</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>B7NZ9272</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Krokus-av sro</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2020-11-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>GeN2</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>wyndhamgardenbaku</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>43853</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>B7NZ9276</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>Krokus-av sro</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>2020-11-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>GeN2</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>wyndhamgardenbaku</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>43852</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>B7NZ9275</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Krokus-av sro</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>2020-11-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>GeN2</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>wyndhamgardenbaku</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>43855</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>B7NZ9273</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Krokus-av sro</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>2020-11-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Passenger Elevator</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>wyndhamgardenbaku</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>№ 43586</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>B7NZ9274</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Krokus-av sro</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>2020-11-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>MonoSpace</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Lor Hospital</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>32101</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>11243372</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>IKMA Lift</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>2011-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>MonoSpace</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Lor Hospital</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>32100</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>11243371</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>IKMA Lift</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>2011-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Schindler 5300</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>"YUSUF" MTK (FALEZ PLAZA)</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>28523</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>IST68180206</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>"S-ENNA" MMC</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>2008-03-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>FHNP</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Mediluks-1</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>43793</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>201802394</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>"S-ENNA" MMC</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>2018-04-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Sərnişin</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Mediluks-1</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>43792</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>AVC 0131</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>"S-ENNA" MMC</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>2018-08-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>HAS</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Dental Vorld B.I MMC</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>35917</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>1838</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Abşeron lift serviz</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>2013-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>C300</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Sərhədçi Servis MMC</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>35881</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>14J01642</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>"S-ENNA" MMC</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>2013-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>c300</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Sərhədçi Servis MMC</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>35879</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>14J01637</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>"S-ENNA" MMC</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>2013-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>C300</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Sərhədçi Servis MMC</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>35875</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>14J01636</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>"S-ENNA" MMC</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>2013-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>C300</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Sərhədçi Servis MMC</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>35876</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>14J01644</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>"S-ENNA" MMC</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>2013-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Passenger PA13(1000)-CO90,09</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Nobel Hotel</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>37838</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Q1NAN186L1</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>"Vertico Service" MMC</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>2017-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>C300</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Sərhədçi Servis MMC</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>35872</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>14J01646</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>"S-ENNA" MMC</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>2013-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>C300</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Sərhədçi Servis MMC</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>35870</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>14J01647</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>"S-ENNA" MMC</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>2013-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>C300</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Sərhədçi Servis MMC</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>35866</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>14J01634</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>"S-ENNA" MMC</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>2013-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>C300</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Sərhədçi Servis MMC</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>35877</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>14J01641</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>"S-ENNA" MMC</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>2013-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>C300</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Sərhədçi Servis MMC</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>35871</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>14J0160</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>"S-ENNA" MMC</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>2013-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>C300</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Sərhədçi Servis MMC</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>35868</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>14J01635</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>"S-ENNA" MMC</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>2013-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>C300</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Sərhədçi Servis MMC</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>35869</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>14J01645</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>"S-ENNA" MMC</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>2013-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>C300</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Sərhədçi Servis MMC</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>35873</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>14J01648</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>"S-ENNA" MMC</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>2013-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>C300</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Sərhədçi Servis MMC</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>35867</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>14J01633</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>"S-ENNA" MMC</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>2013-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>C300</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Sərhədçi Servis MMC</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>35880</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>14J01639</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>"S-ENNA" MMC</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>2013-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>C300</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Sərhədçi Servis MMC</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>35874</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>14J01638</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>"S-ENNA" MMC</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>2013-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Sərnişin GRPS20-1000/1.0-MR</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Referans Medi-Art Hospital MMC</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>RH95347</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>RH95347</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>STAR İN MMC</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>C300</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Sərhədçi Servis MMC</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>35878</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>14j01643</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>"S-ENNA" MMC</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>2014-03-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Makine daireli</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Qarabağ müharibəsi əlilləri və şəhid ailələri üçün inşa edilmiş yaşayış binası</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>44582</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>244524</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>ECO SYSTEM MMC</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>2019-04-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Qarabağ müharibəsi əlilləri və şəhid ailələri üçün inşa edilmiş yaşayış binası</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>44585</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>244527</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>ECO SYSTEM MMC</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>2019-04-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Makine daireli</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Qarabağ müharibəsi əlilləri və şəhid ailələri üçün inşa edilmiş yaşayış binası</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>44584</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>244526</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>ECO SYSTEM MMC</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>2019-04-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Makine daireli</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Qarabağ müharibəsi əlilləri və şəhid ailələri üçün inşa edilmiş yaşayış binası</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>44587</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>244529</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>ECO SYSTEM MMC</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>2019-04-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Makine daireli</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Qarabağ müharibəsi əlilləri və şəhid ailələri üçün inşa edilmiş yaşayış binası</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>44583</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>244525</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>ECO SYSTEM MMC</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>2019-04-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Makine daireli</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Qarabağ müharibəsi əlilləri və şəhid ailələri üçün inşa edilmiş yaşayış binası</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>44586</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>244528</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>ECO SYSTEM MMC</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>2019-04-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Passenger Elevator</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ASG Business Aviation - “Təmir və Texniki Qulluq Xidməti” nin inzibati binasında </t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>29679</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>8545</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>FM Technics MMC</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>2008-01-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Di1-PA08(0630)-060 - 3/3</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>ASG Business Aviation - “Baku Logistics Center”, blok "D" saylı inzibati binası</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>29327</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>2004BE 1324E01 L3</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>Krokus-av sro</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>2004-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Di1-PA08(0630)-060 - 3/3</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>ASG Business Aviation - “Baku Logistics Center”,  blok "C" saylı inzibati binası</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>29326</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>2004BE 1324E01 L2</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>Krokus-av sro</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>2004-09-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>ELENESSA</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Təməl-2012</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>45568</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>23EXE10-530-8</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>“MELCO ELEVATOR AZERBAIJAN” MMC</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>2023-04-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>ELENESSA</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Təməl-2012</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>45567</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>23EXE10-530-7</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>“MELCO ELEVATOR AZERBAIJAN” MMC</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>2023-04-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>ELENESSA</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Təməl-2012</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>45566</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>23EXE10-530-6</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>“MELCO ELEVATOR AZERBAIJAN” MMC</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>2023-04-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>ELENESSA</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Təməl-2012</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>45565</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>23EXE10-530-5</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>“MELCO ELEVATOR AZERBAIJAN” MMC</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>2023-04-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>ELENESSA</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Təməl-2012</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>45564</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>23EXE10-530-4</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>“MELCO ELEVATOR AZERBAIJAN” MMC</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>2023-04-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>ELENESSA</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Təməl-2012</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>45563</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>23EXE10-530-3</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>“MELCO ELEVATOR AZERBAIJAN” MMC</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>2023-04-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>ELENESSA</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Təməl-2012</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>45562</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>23EXE10-530-2</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>“MELCO ELEVATOR AZERBAIJAN” MMC</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>2023-04-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>ELENESSA</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Təməl-2012</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>45561</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>23EXE10-530-1</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>“MELCO ELEVATOR AZERBAIJAN” MMC</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>2023-04-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>GQXL2P</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Park Hill Tower</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>44242</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>E-OB-94301</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>“MELCO ELEVATOR AZERBAIJAN” MMC</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>2022-01-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>GQXL2P</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Park Hill Tower</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>42600</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>E-XE-X3102</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>“MELCO ELEVATOR AZERBAIJAN” MMC</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>2020-11-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>GQXL2P</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Park Hill Tower</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>42599</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>E-XE-X3101</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>“MELCO ELEVATOR AZERBAIJAN” MMC</t>
+        </is>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>2020-11-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>GQXL2P</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Park Hill Tower</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>42257</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>E-XE-X3103</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>“MELCO ELEVATOR AZERBAIJAN” MMC</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>2020-11-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>NEXIEZ-MRL GQXL2</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>Park Hill Terrace</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>45321</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>E-OB-87108</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>“MELCO ELEVATOR AZERBAIJAN” MMC</t>
+        </is>
+      </c>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>2022-01-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>Teatro Boutuqe Hotel</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>34871</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>YKS-Az-135</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>GİPFEL ELEVATOR and ESCALATOR MMC</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>2011-04-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>NEXIEZ-MRL GQXL2</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>Park Hill Terrace</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>45314</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>E-OB-87107</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>“MELCO ELEVATOR AZERBAIJAN” MMC</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>2022-01-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>NEXIEZ-MRL GQXL2</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Park Hill Terrace</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>45315</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>E-OB-87106</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>“MELCO ELEVATOR AZERBAIJAN” MMC</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>2022-01-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>NEXIEZ-MRL GQXL2</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>Park Hill Terrace</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>45317</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>E-OB-87105</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>“MELCO ELEVATOR AZERBAIJAN” MMC</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>2022-01-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>Teatro Boutuqe Hotel</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>34872</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>YKS-Az-141</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>GİPFEL ELEVATOR and ESCALATOR MMC</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>2011-04-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>GQXL2P</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>Park Hill Tower</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>44243</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>E-OB-94302</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>“MELCO ELEVATOR AZERBAIJAN” MMC</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>2021-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>NEXIEZ-MRL GQXL2</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>Park Hill Terrace</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>45316</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>E-OB-87104</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>“MELCO ELEVATOR AZERBAIJAN” MMC</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>2022-01-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>NEXIEZ-MRL GQXL2</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>Park Hill Terrace</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>45319</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>E-OB-87103</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>“MELCO ELEVATOR AZERBAIJAN” MMC</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>2022-01-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>NEXIEZ-MRL GQXL2</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>Park Hill Terrace</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>45318</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>E-OB-87102</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>“MELCO ELEVATOR AZERBAIJAN” MMC</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>2022-01-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Passenger Elevator</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Saf clinic</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>45155</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>AYG15012</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>"PREMİUM R.E" MMC</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>2023-08-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="4" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>NEXIEZ-MRL GQXL2</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>Park Hill Terrace</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>45320</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>E-OB-87101</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>onreview_government</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>“MELCO ELEVATOR AZERBAIJAN” MMC</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>2022-01-31</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/onreview_lifts.xlsx
+++ b/onreview_lifts.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -524,22 +524,22 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>MR</t>
+          <t>GPR-PA10(800)-2CO60-07/07</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Bərəkət-6 MTK</t>
+          <t xml:space="preserve"> "AURUS HOTEL" MMC </t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>17916</t>
+          <t>38439</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>SRL2019-1221</t>
+          <t>Q1NAP281</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2019-12-09</t>
+          <t>2018-03-05</t>
         </is>
       </c>
     </row>
@@ -574,12 +574,12 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>17918</t>
+          <t>17916</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>SRL2019-1219</t>
+          <t>SRL2019-1221</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
@@ -614,12 +614,12 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>17917</t>
+          <t>17918</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>SRL2019-1220</t>
+          <t>SRL2019-1219</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -644,22 +644,22 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Passenger Elevator</t>
+          <t>MR</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Golden Coast Hotel</t>
+          <t>Bərəkət-6 MTK</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">28600       </t>
+          <t>17917</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>2005BE2305E02 Lift 3</t>
+          <t>SRL2019-1220</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -669,12 +669,12 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>“EXPO-LIFT” MMC</t>
+          <t>ECO SYSTEM MMC</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>2005-12-21</t>
+          <t>2019-12-09</t>
         </is>
       </c>
     </row>
@@ -694,12 +694,12 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28599      </t>
+          <t xml:space="preserve">28600       </t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>2005BE2305E01 Lift1</t>
+          <t>2005BE2305E02 Lift 3</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
@@ -734,12 +734,12 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">28598    </t>
+          <t xml:space="preserve">28599      </t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>2005BE2305E01 Lift 2</t>
+          <t>2005BE2305E01 Lift1</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -764,22 +764,22 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>GQXL2P</t>
+          <t>Passenger Elevator</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Diamed</t>
+          <t>Golden Coast Hotel</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>34221</t>
+          <t xml:space="preserve">28598    </t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>EY2G5801</t>
+          <t>2005BE2305E01 Lift 2</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -789,12 +789,12 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>“MELCO ELEVATOR AZERBAIJAN” MMC</t>
+          <t>“EXPO-LIFT” MMC</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>2013-07-09</t>
+          <t>2005-12-21</t>
         </is>
       </c>
     </row>
@@ -804,22 +804,22 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>GeN2</t>
+          <t>GQXL2P</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>wyndhamgardenbaku</t>
+          <t>Diamed</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>43854</t>
+          <t>34221</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>B7NZ9272</t>
+          <t>EY2G5801</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Krokus-av sro</t>
+          <t>“MELCO ELEVATOR AZERBAIJAN” MMC</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>2020-11-13</t>
+          <t>2013-07-09</t>
         </is>
       </c>
     </row>
@@ -884,7 +884,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>GeN2</t>
+          <t>Passenger Elevator</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>43853</t>
+          <t>43856</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>B7NZ9276</t>
+          <t>B7NZ9274</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>2020-11-13</t>
+          <t>2020-11-14</t>
         </is>
       </c>
     </row>
@@ -924,22 +924,22 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>GeN2</t>
+          <t>MonoSpace</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>wyndhamgardenbaku</t>
+          <t>Lor Hospital</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>43852</t>
+          <t>32101</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>B7NZ9275</t>
+          <t>11243372</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>Krokus-av sro</t>
+          <t>IKMA Lift</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>2020-11-14</t>
+          <t>2011-12-31</t>
         </is>
       </c>
     </row>
@@ -964,22 +964,22 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>GeN2</t>
+          <t>MonoSpace</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>wyndhamgardenbaku</t>
+          <t>Lor Hospital</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>43855</t>
+          <t>32100</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>B7NZ9273</t>
+          <t>11243371</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -989,12 +989,12 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Krokus-av sro</t>
+          <t>IKMA Lift</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>2020-11-14</t>
+          <t>2011-12-31</t>
         </is>
       </c>
     </row>
@@ -1004,22 +1004,22 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Passenger Elevator</t>
+          <t>Makine daireli</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>wyndhamgardenbaku</t>
+          <t>Qarabağ müharibəsi əlilləri və şəhid ailələri üçün inşa edilmiş yaşayış binası</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>№ 43586</t>
+          <t>44582</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>B7NZ9274</t>
+          <t>244524</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>Krokus-av sro</t>
+          <t>ECO SYSTEM MMC</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>2020-11-14</t>
+          <t>2019-04-01</t>
         </is>
       </c>
     </row>
@@ -1044,22 +1044,22 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>MonoSpace</t>
+          <t>MR</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Lor Hospital</t>
+          <t>Qarabağ müharibəsi əlilləri və şəhid ailələri üçün inşa edilmiş yaşayış binası</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>32101</t>
+          <t>44585</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>11243372</t>
+          <t>244527</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -1069,12 +1069,12 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>IKMA Lift</t>
+          <t>ECO SYSTEM MMC</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>2011-12-31</t>
+          <t>2019-04-01</t>
         </is>
       </c>
     </row>
@@ -1084,22 +1084,22 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>MonoSpace</t>
+          <t>Makine daireli</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Lor Hospital</t>
+          <t>Qarabağ müharibəsi əlilləri və şəhid ailələri üçün inşa edilmiş yaşayış binası</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>32100</t>
+          <t>44584</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>11243371</t>
+          <t>244526</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>IKMA Lift</t>
+          <t>ECO SYSTEM MMC</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>2011-12-31</t>
+          <t>2019-04-01</t>
         </is>
       </c>
     </row>
@@ -1134,12 +1134,12 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>44582</t>
+          <t>44587</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>244524</t>
+          <t>244529</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>MR</t>
+          <t>Makine daireli</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>44585</t>
+          <t>44583</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>244527</t>
+          <t>244525</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -1214,12 +1214,12 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>44584</t>
+          <t>44586</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>244526</t>
+          <t>244528</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -1244,22 +1244,22 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Makine daireli</t>
+          <t>Passenger Elevator</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Qarabağ müharibəsi əlilləri və şəhid ailələri üçün inşa edilmiş yaşayış binası</t>
+          <t xml:space="preserve">ASG Business Aviation - “Təmir və Texniki Qulluq Xidməti” nin inzibati binasında </t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>44587</t>
+          <t>29679</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>244529</t>
+          <t>8545</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>ECO SYSTEM MMC</t>
+          <t>FM Technics MMC</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>2019-04-01</t>
+          <t>2008-01-03</t>
         </is>
       </c>
     </row>
@@ -1284,22 +1284,22 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Makine daireli</t>
+          <t>Passenger Elevator</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Qarabağ müharibəsi əlilləri və şəhid ailələri üçün inşa edilmiş yaşayış binası</t>
+          <t>Saf clinic</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>44583</t>
+          <t>45155</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>244525</t>
+          <t>AYG15012</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -1309,172 +1309,12 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>ECO SYSTEM MMC</t>
+          <t>"PREMİUM R.E" MMC</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>2019-04-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Makine daireli</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Qarabağ müharibəsi əlilləri və şəhid ailələri üçün inşa edilmiş yaşayış binası</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>44586</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>244528</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>onreview_government</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>ECO SYSTEM MMC</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>2019-04-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Passenger Elevator</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ASG Business Aviation - “Təmir və Texniki Qulluq Xidməti” nin inzibati binasında </t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>29679</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>8545</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>onreview_government</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>FM Technics MMC</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>2008-01-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Passenger Elevator</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>Saf clinic</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>45155</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>AYG15012</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>onreview_government</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>"PREMİUM R.E" MMC</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
           <t>2023-08-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>schindler3300AP</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>life Estate MMC</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40365 </t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>İST0011187666</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>onreview_government</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>Bakı Mexanika və Elektronika MMC</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>2018-04-14</t>
         </is>
       </c>
     </row>
